--- a/docs/5_기능정의서/기능정의서.xlsx
+++ b/docs/5_기능정의서/기능정의서.xlsx
@@ -5,11 +5,11 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\개인\서류\5_기능정의서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\zzz\withyou\docs\5_기능정의서\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11460" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="17715" windowHeight="6330" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Sheet1" sheetId="1" r:id="rId4"/>
@@ -19,59 +19,195 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <x:si>
-    <x:t>화면 ID / 명</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>1.아이디 5회 오류 시 계정 잠금</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>SCR-001 / 로그인 페이지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2. 미입력 시 안내 메시지 출력</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="63">
+  <x:si>
+    <x:t>DB와 대조하여 일치 여부 확인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCR-009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>회원가입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페이징 버튼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지도 API로 위치 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로그인 성공 시 로그인 화면 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로필 정보 수정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비고</x:t>
   </x:si>
   <x:si>
     <x:t>구분</x:t>
   </x:si>
   <x:si>
-    <x:t>비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내용</x:t>
-  </x:si>
-  <x:si>
     <x:t>기능명</x:t>
   </x:si>
   <x:si>
+    <x:t>SCR-005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검색된 내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문제 은행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCR-010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>답안 작성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCR-007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCR-008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필터 적용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마이페이지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계정 탈퇴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCR-006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계정찾기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCR-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCR-004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCR-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCR-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메시지 인증 실패 메시지 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기능 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비밀번호 암호화 비교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디, 비밀번호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수업 정보 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가입 여부 메시지 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>출력/결과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>입력 데이터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예외 처리</x:t>
+  </x:si>
+  <x:si>
     <x:t>핵심 로직</x:t>
   </x:si>
   <x:si>
-    <x:t>입력 데이터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>출력/결과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디(Email), 비밀번호(PW)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. DB와 대조하여 일치 여부 확인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2. 비밀번호 암호화 비교</x:t>
-  </x:si>
-  <x:si>
     <x:t>로그인 성공 시 메인 화면(SCR-002) 이동</x:t>
   </x:si>
   <x:si>
-    <x:t>예외 처리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사용자 인증 및 로그인</x:t>
+    <x:t>답안 유효성 체크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시험</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필수값 미입력 시 안내 메시지 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중복 여부 메시지 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디/비밀번호 로그인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미입력 시 안내 메시지 출력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이름, 비밀번호, 전화번호, 학년, 이메일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가입 여부 확인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인증 메시지 전송</x:t>
+  </x:si>
+  <x:si>
+    <x:t>학원 정보 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DB에 정보 입력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>입력값 유효성 검사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전화번호 인증 실패</x:t>
+  </x:si>
+  <x:si>
+    <x:t>답안 내용 제출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전화번호, 아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비로그인시 로그인 화면 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이름, 전화번호, 이메일, 학년</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가입된 아이디 표시, 인증 메시지 전송</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검색 키워드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>디테인 페이지 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로필 정보 및 비밀번호 수정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지사항</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -165,11 +301,8 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="8">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -953,114 +1086,672 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="B2:D23"/>
+  <x:dimension ref="B2:AF32"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="2" max="2" width="14" customWidth="1"/>
     <x:col min="3" max="3" width="38.25" customWidth="1"/>
     <x:col min="4" max="4" width="12.375" customWidth="1"/>
+    <x:col min="6" max="6" width="10.8984375" bestFit="1" customWidth="1"/>
+    <x:col min="7" max="7" width="24.375" customWidth="1"/>
+    <x:col min="10" max="10" width="10.8984375" bestFit="1" customWidth="1"/>
+    <x:col min="11" max="11" width="25.875" bestFit="1" customWidth="1"/>
+    <x:col min="14" max="14" width="10.8984375" bestFit="1" customWidth="1"/>
+    <x:col min="15" max="15" width="25.875" bestFit="1" customWidth="1"/>
+    <x:col min="18" max="18" width="10.8984375" bestFit="1" customWidth="1"/>
+    <x:col min="19" max="19" width="19.125" customWidth="1"/>
+    <x:col min="22" max="22" width="10.8984375" bestFit="1" customWidth="1"/>
+    <x:col min="23" max="23" width="23.32421875" bestFit="1" customWidth="1"/>
+    <x:col min="26" max="26" width="10.8984375" bestFit="1" customWidth="1"/>
+    <x:col min="27" max="27" width="17.11328125" bestFit="1" customWidth="1"/>
+    <x:col min="30" max="30" width="10.8984375" bestFit="1" customWidth="1"/>
+    <x:col min="31" max="31" width="17.11328125" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="2" spans="2:4">
-      <x:c r="B2" s="5" t="s">
+    <x:row r="2" spans="2:32">
+      <x:c r="B2" s="4" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C2" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D2" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F2" s="4" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G2" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H2" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J2" s="4" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K2" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L2" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N2" s="4" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="O2" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P2" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="R2" s="4" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="S2" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="T2" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="V2" s="4" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="W2" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="X2" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Z2" s="4" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AA2" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="AB2" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="AD2" s="4" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AE2" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="AF2" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="2:32">
+      <x:c r="B3" s="5" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D3" s="3"/>
+      <x:c r="F3" s="5" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G3" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H3" s="3"/>
+      <x:c r="J3" s="5" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K3" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L3" s="3"/>
+      <x:c r="N3" s="5" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="O3" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="P3" s="3"/>
+      <x:c r="R3" s="5" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="S3" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="T3" s="3"/>
+      <x:c r="V3" s="5" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="W3" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="X3" s="3"/>
+      <x:c r="Z3" s="5" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="AA3" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB3" s="3"/>
+      <x:c r="AD3" s="5" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="AE3" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="AF3" s="3"/>
+    </x:row>
+    <x:row r="4" spans="2:32">
+      <x:c r="B4" s="5" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D4" s="3"/>
+      <x:c r="F4" s="5" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G4" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H4" s="3"/>
+      <x:c r="J4" s="5" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="K4" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L4" s="3"/>
+      <x:c r="N4" s="5" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="O4" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P4" s="3"/>
+      <x:c r="R4" s="5" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="S4" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="T4" s="3"/>
+      <x:c r="V4" s="5" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="W4" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="X4" s="3"/>
+      <x:c r="Z4" s="5" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="AA4" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="AB4" s="3"/>
+      <x:c r="AD4" s="5" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="AE4" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="AF4" s="3"/>
+    </x:row>
+    <x:row r="5" spans="2:32">
+      <x:c r="B5" s="5" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D5" s="3"/>
+      <x:c r="F5" s="5" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G5" s="2"/>
+      <x:c r="H5" s="3"/>
+      <x:c r="J5" s="5" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="K5" s="2" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L5" s="3"/>
+      <x:c r="N5" s="5" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="O5" s="2"/>
+      <x:c r="P5" s="3"/>
+      <x:c r="R5" s="5" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="S5" s="2"/>
+      <x:c r="T5" s="3"/>
+      <x:c r="V5" s="5" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="W5" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="X5" s="3"/>
+      <x:c r="Z5" s="5" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="AA5" s="2"/>
+      <x:c r="AB5" s="3"/>
+      <x:c r="AD5" s="5" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="AE5" s="2" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="AF5" s="3"/>
+    </x:row>
+    <x:row r="6" spans="2:32">
+      <x:c r="B6" s="5" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C6" s="2" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D6" s="3"/>
+      <x:c r="F6" s="5" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G6" s="2"/>
+      <x:c r="H6" s="3"/>
+      <x:c r="J6" s="5" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K6" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L6" s="3"/>
+      <x:c r="N6" s="5" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="O6" s="2"/>
+      <x:c r="P6" s="3"/>
+      <x:c r="R6" s="5" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="S6" s="2"/>
+      <x:c r="T6" s="3"/>
+      <x:c r="V6" s="5" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="W6" s="2"/>
+      <x:c r="X6" s="3"/>
+      <x:c r="Z6" s="5" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="AA6" s="2"/>
+      <x:c r="AB6" s="3"/>
+      <x:c r="AD6" s="5" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="AE6" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="AF6" s="3"/>
+    </x:row>
+    <x:row r="7" spans="2:32">
+      <x:c r="B7" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D7" s="3"/>
+      <x:c r="F7" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G7" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H7" s="3"/>
+      <x:c r="J7" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K7" s="2" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L7" s="3"/>
+      <x:c r="N7" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="O7" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P7" s="3"/>
+      <x:c r="R7" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="S7" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="T7" s="3"/>
+      <x:c r="V7" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="W7" s="2" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="X7" s="3"/>
+      <x:c r="Z7" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="AA7" s="2" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AB7" s="3"/>
+      <x:c r="AD7" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="AE7" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="AF7" s="3"/>
+    </x:row>
+    <x:row r="8" spans="2:32">
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="2" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D8" s="3"/>
+      <x:c r="F8" s="7"/>
+      <x:c r="G8" s="2"/>
+      <x:c r="H8" s="3"/>
+      <x:c r="J8" s="7"/>
+      <x:c r="K8" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L8" s="3"/>
+      <x:c r="N8" s="7"/>
+      <x:c r="O8" s="2"/>
+      <x:c r="P8" s="3"/>
+      <x:c r="R8" s="7"/>
+      <x:c r="S8" s="2"/>
+      <x:c r="T8" s="3"/>
+      <x:c r="V8" s="7"/>
+      <x:c r="W8" s="2" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="X8" s="3"/>
+      <x:c r="Z8" s="7"/>
+      <x:c r="AA8" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C2" s="5" t="s">
+      <x:c r="AB8" s="3"/>
+      <x:c r="AD8" s="7"/>
+      <x:c r="AE8" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="AF8" s="3"/>
+    </x:row>
+    <x:row r="9" spans="2:32">
+      <x:c r="B9" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D9" s="3"/>
+      <x:c r="F9" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G9" s="1"/>
+      <x:c r="H9" s="3"/>
+      <x:c r="J9" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="K9" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="L9" s="3"/>
+      <x:c r="N9" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="O9" s="1"/>
+      <x:c r="P9" s="3"/>
+      <x:c r="R9" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="S9" s="1"/>
+      <x:c r="T9" s="3"/>
+      <x:c r="V9" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="W9" s="1"/>
+      <x:c r="X9" s="3"/>
+      <x:c r="Z9" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="AA9" s="1"/>
+      <x:c r="AB9" s="3"/>
+      <x:c r="AD9" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="AE9" s="1"/>
+      <x:c r="AF9" s="3"/>
+    </x:row>
+    <x:row r="10" spans="2:32">
+      <x:c r="B10" s="6"/>
+      <x:c r="C10" s="2" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D10" s="3"/>
+      <x:c r="F10" s="7"/>
+      <x:c r="G10" s="2"/>
+      <x:c r="H10" s="3"/>
+      <x:c r="J10" s="7"/>
+      <x:c r="K10" s="2"/>
+      <x:c r="L10" s="3"/>
+      <x:c r="N10" s="7"/>
+      <x:c r="O10" s="2"/>
+      <x:c r="P10" s="3"/>
+      <x:c r="R10" s="7"/>
+      <x:c r="S10" s="2"/>
+      <x:c r="T10" s="3"/>
+      <x:c r="V10" s="7"/>
+      <x:c r="W10" s="2"/>
+      <x:c r="X10" s="3"/>
+      <x:c r="Z10" s="7"/>
+      <x:c r="AA10" s="2"/>
+      <x:c r="AB10" s="3"/>
+      <x:c r="AD10" s="7"/>
+      <x:c r="AE10" s="2"/>
+      <x:c r="AF10" s="3"/>
+    </x:row>
+    <x:row r="12" spans="2:2">
+      <x:c r="B12" s="1"/>
+    </x:row>
+    <x:row r="13" spans="2:4">
+      <x:c r="B13" s="4" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C13" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="2:4">
+      <x:c r="B14" s="5" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C14" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D14" s="3"/>
+    </x:row>
+    <x:row r="15" spans="2:4">
+      <x:c r="B15" s="5" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D15" s="3"/>
+    </x:row>
+    <x:row r="16" spans="2:4">
+      <x:c r="B16" s="5" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C16" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D16" s="3"/>
+    </x:row>
+    <x:row r="17" spans="2:4">
+      <x:c r="B17" s="5" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C17" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D2" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="2:4">
-      <x:c r="B3" s="6" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="4"/>
-    </x:row>
-    <x:row r="4" spans="2:4">
-      <x:c r="B4" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D4" s="4"/>
-    </x:row>
-    <x:row r="5" spans="2:4">
-      <x:c r="B5" s="6" t="s">
+      <x:c r="D17" s="3"/>
+    </x:row>
+    <x:row r="18" spans="2:4">
+      <x:c r="B18" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C18" s="2" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D18" s="3"/>
+    </x:row>
+    <x:row r="19" spans="2:4">
+      <x:c r="B19" s="7"/>
+      <x:c r="C19" s="2" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D19" s="3"/>
+    </x:row>
+    <x:row r="20" spans="2:4">
+      <x:c r="B20" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D20" s="3"/>
+    </x:row>
+    <x:row r="21" spans="2:4">
+      <x:c r="B21" s="7"/>
+      <x:c r="C21" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D21" s="3"/>
+    </x:row>
+    <x:row r="23" spans="2:2">
+      <x:c r="B23" s="1"/>
+    </x:row>
+    <x:row r="24" spans="2:4">
+      <x:c r="B24" s="4" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C24" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D24" s="4" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C5" s="3" t="s">
+    </x:row>
+    <x:row r="25" spans="2:4">
+      <x:c r="B25" s="5" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C25" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D25" s="3"/>
+    </x:row>
+    <x:row r="26" spans="2:4">
+      <x:c r="B26" s="5" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D5" s="4"/>
-    </x:row>
-    <x:row r="6" spans="2:4">
-      <x:c r="B6" s="6" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C6" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="4"/>
-    </x:row>
-    <x:row r="7" spans="2:4">
-      <x:c r="B7" s="7" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7" s="3" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D7" s="4"/>
-    </x:row>
-    <x:row r="8" spans="2:4">
-      <x:c r="B8" s="8"/>
-      <x:c r="C8" s="3" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D8" s="4"/>
-    </x:row>
-    <x:row r="9" spans="2:4">
-      <x:c r="B9" s="7" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="4"/>
-    </x:row>
-    <x:row r="10" spans="2:4">
-      <x:c r="B10" s="8"/>
-      <x:c r="C10" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="4"/>
-    </x:row>
-    <x:row r="12" spans="2:2">
-      <x:c r="B12" s="2"/>
-    </x:row>
-    <x:row r="16" spans="2:2">
-      <x:c r="B16" s="1"/>
-    </x:row>
-    <x:row r="18" spans="2:2">
-      <x:c r="B18" s="2"/>
-    </x:row>
-    <x:row r="20" spans="2:2">
-      <x:c r="B20" s="2"/>
-    </x:row>
-    <x:row r="23" spans="2:2">
-      <x:c r="B23" s="2"/>
+      <x:c r="C26" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D26" s="3"/>
+    </x:row>
+    <x:row r="27" spans="2:4">
+      <x:c r="B27" s="5" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C27" s="2" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D27" s="3"/>
+    </x:row>
+    <x:row r="28" spans="2:4">
+      <x:c r="B28" s="5" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C28" s="2" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D28" s="3"/>
+    </x:row>
+    <x:row r="29" spans="2:4">
+      <x:c r="B29" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C29" s="2" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D29" s="3"/>
+    </x:row>
+    <x:row r="30" spans="2:4">
+      <x:c r="B30" s="7"/>
+      <x:c r="C30" s="2" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D30" s="3"/>
+    </x:row>
+    <x:row r="31" spans="2:4">
+      <x:c r="B31" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D31" s="3"/>
+    </x:row>
+    <x:row r="32" spans="2:4">
+      <x:c r="B32" s="7"/>
+      <x:c r="C32" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D32" s="3"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="2">
+  <x:mergeCells count="20">
     <x:mergeCell ref="B7:B8"/>
+    <x:mergeCell ref="F7:F8"/>
+    <x:mergeCell ref="J7:J8"/>
+    <x:mergeCell ref="N7:N8"/>
+    <x:mergeCell ref="R7:R8"/>
+    <x:mergeCell ref="V7:V8"/>
+    <x:mergeCell ref="Z7:Z8"/>
+    <x:mergeCell ref="AD7:AD8"/>
     <x:mergeCell ref="B9:B10"/>
+    <x:mergeCell ref="F9:F10"/>
+    <x:mergeCell ref="J9:J10"/>
+    <x:mergeCell ref="N9:N10"/>
+    <x:mergeCell ref="R9:R10"/>
+    <x:mergeCell ref="V9:V10"/>
+    <x:mergeCell ref="Z9:Z10"/>
+    <x:mergeCell ref="AD9:AD10"/>
+    <x:mergeCell ref="B18:B19"/>
+    <x:mergeCell ref="B20:B21"/>
+    <x:mergeCell ref="B29:B30"/>
+    <x:mergeCell ref="B31:B32"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
--- a/docs/5_기능정의서/기능정의서.xlsx
+++ b/docs/5_기능정의서/기능정의서.xlsx
@@ -21,193 +21,193 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="63">
   <x:si>
+    <x:t>SCR-005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계정 탈퇴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문제 은행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>답안 작성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCR-006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>회원가입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>페이징 버튼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검색된 내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCR-010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCR-007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCR-008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCR-009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필터 적용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마이페이지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>출력/결과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCR-004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검색 키워드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCR-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기능 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCR-003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCR-002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예외 처리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공지사항</x:t>
+  </x:si>
+  <x:si>
+    <x:t>입력 데이터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핵심 로직</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계정찾기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필수값 미입력 시 안내 메시지 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이름, 전화번호, 이메일, 학년</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메시지 인증 실패 메시지 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로그인 성공 시 로그인 화면 이동</x:t>
+  </x:si>
+  <x:si>
     <x:t>DB와 대조하여 일치 여부 확인</x:t>
   </x:si>
   <x:si>
-    <x:t>SCR-009</x:t>
+    <x:t>프로필 정보 및 비밀번호 수정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비밀번호 암호화 비교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수업 정보 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디, 비밀번호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인증 메시지 전송</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전화번호, 아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>답안 유효성 체크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>학원 정보 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DB에 정보 입력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>입력값 유효성 검사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가입 여부 확인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>답안 내용 제출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전화번호 인증 실패</x:t>
+  </x:si>
+  <x:si>
+    <x:t>디테인 페이지 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로필 정보 수정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가입된 아이디 표시, 인증 메시지 전송</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이름, 비밀번호, 전화번호, 학년, 이메일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중복 여부 메시지 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비로그인시 로그인 화면 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미입력 시 안내 메시지 출력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지도 API로 위치 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가입 여부 메시지 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디/비밀번호 로그인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수업</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
   </x:si>
   <x:si>
     <x:t>메인</x:t>
   </x:si>
   <x:si>
-    <x:t>회원가입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>페이징 버튼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지도 API로 위치 표시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로그인 성공 시 로그인 화면 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로필 정보 수정</x:t>
+    <x:t>기능명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시험</x:t>
   </x:si>
   <x:si>
     <x:t>내용</x:t>
   </x:si>
   <x:si>
-    <x:t>비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기능명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCR-005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검색된 내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문제 은행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCR-010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>답안 작성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCR-007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCR-008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필터 적용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마이페이지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계정 탈퇴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCR-006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계정찾기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCR-003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCR-004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCR-002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCR-001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메시지 인증 실패 메시지 표시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기능 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비밀번호 암호화 비교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디, 비밀번호</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수업 정보 표시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가입 여부 메시지 표시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>출력/결과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>입력 데이터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예외 처리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>핵심 로직</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로그인 성공 시 메인 화면(SCR-002) 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>답안 유효성 체크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시험</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필수값 미입력 시 안내 메시지 표시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중복 여부 메시지 표시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디/비밀번호 로그인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미입력 시 안내 메시지 출력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이름, 비밀번호, 전화번호, 학년, 이메일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가입 여부 확인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인증 메시지 전송</x:t>
-  </x:si>
-  <x:si>
-    <x:t>학원 정보 표시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DB에 정보 입력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>입력값 유효성 검사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전화번호 인증 실패</x:t>
-  </x:si>
-  <x:si>
-    <x:t>답안 내용 제출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전화번호, 아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수업</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비로그인시 로그인 화면 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이름, 전화번호, 이메일, 학년</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가입된 아이디 표시, 인증 메시지 전송</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검색 키워드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>디테인 페이지 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로필 정보 및 비밀번호 수정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공지사항</x:t>
+    <x:t>로그인 성공 시 메인 화면 이동</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1110,354 +1110,354 @@
   <x:sheetData>
     <x:row r="2" spans="2:32">
       <x:c r="B2" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C2" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D2" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F2" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G2" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H2" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J2" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="K2" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="L2" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N2" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="O2" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="P2" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="R2" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="S2" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="T2" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="V2" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="W2" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="X2" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Z2" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AA2" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AB2" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AD2" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AE2" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AF2" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="2:32">
       <x:c r="B3" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D3" s="3"/>
       <x:c r="F3" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H3" s="3"/>
       <x:c r="J3" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K3" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L3" s="3"/>
       <x:c r="N3" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="O3" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="P3" s="3"/>
       <x:c r="R3" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="S3" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="T3" s="3"/>
       <x:c r="V3" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="W3" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="X3" s="3"/>
       <x:c r="Z3" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AA3" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="AB3" s="3"/>
       <x:c r="AD3" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AE3" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="AF3" s="3"/>
     </x:row>
     <x:row r="4" spans="2:32">
       <x:c r="B4" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D4" s="3"/>
       <x:c r="F4" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H4" s="3"/>
       <x:c r="J4" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L4" s="3"/>
       <x:c r="N4" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O4" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="P4" s="3"/>
       <x:c r="R4" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="S4" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="T4" s="3"/>
       <x:c r="V4" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="W4" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="X4" s="3"/>
       <x:c r="Z4" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AA4" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="AB4" s="3"/>
       <x:c r="AD4" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AE4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AF4" s="3"/>
     </x:row>
     <x:row r="5" spans="2:32">
       <x:c r="B5" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D5" s="3"/>
       <x:c r="F5" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G5" s="2"/>
       <x:c r="H5" s="3"/>
       <x:c r="J5" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="K5" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L5" s="3"/>
       <x:c r="N5" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="O5" s="2"/>
       <x:c r="P5" s="3"/>
       <x:c r="R5" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S5" s="2"/>
       <x:c r="T5" s="3"/>
       <x:c r="V5" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="W5" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="X5" s="3"/>
       <x:c r="Z5" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="AA5" s="2"/>
       <x:c r="AB5" s="3"/>
       <x:c r="AD5" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="AE5" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="AF5" s="3"/>
     </x:row>
     <x:row r="6" spans="2:32">
       <x:c r="B6" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D6" s="3"/>
       <x:c r="F6" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G6" s="2"/>
       <x:c r="H6" s="3"/>
       <x:c r="J6" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K6" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="L6" s="3"/>
       <x:c r="N6" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="O6" s="2"/>
       <x:c r="P6" s="3"/>
       <x:c r="R6" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="S6" s="2"/>
       <x:c r="T6" s="3"/>
       <x:c r="V6" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="W6" s="2"/>
       <x:c r="X6" s="3"/>
       <x:c r="Z6" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="AA6" s="2"/>
       <x:c r="AB6" s="3"/>
       <x:c r="AD6" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="AE6" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AF6" s="3"/>
     </x:row>
     <x:row r="7" spans="2:32">
       <x:c r="B7" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D7" s="3"/>
       <x:c r="F7" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G7" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H7" s="3"/>
       <x:c r="J7" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K7" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="L7" s="3"/>
       <x:c r="N7" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="O7" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="P7" s="3"/>
       <x:c r="R7" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="S7" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="T7" s="3"/>
       <x:c r="V7" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="W7" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="X7" s="3"/>
       <x:c r="Z7" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="AA7" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AB7" s="3"/>
       <x:c r="AD7" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="AE7" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="AF7" s="3"/>
     </x:row>
     <x:row r="8" spans="2:32">
       <x:c r="B8" s="6"/>
       <x:c r="C8" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D8" s="3"/>
       <x:c r="F8" s="7"/>
@@ -1465,7 +1465,7 @@
       <x:c r="H8" s="3"/>
       <x:c r="J8" s="7"/>
       <x:c r="K8" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L8" s="3"/>
       <x:c r="N8" s="7"/>
@@ -1476,62 +1476,62 @@
       <x:c r="T8" s="3"/>
       <x:c r="V8" s="7"/>
       <x:c r="W8" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="X8" s="3"/>
       <x:c r="Z8" s="7"/>
       <x:c r="AA8" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AB8" s="3"/>
       <x:c r="AD8" s="7"/>
       <x:c r="AE8" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AF8" s="3"/>
     </x:row>
     <x:row r="9" spans="2:32">
       <x:c r="B9" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D9" s="3"/>
       <x:c r="F9" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G9" s="1"/>
       <x:c r="H9" s="3"/>
       <x:c r="J9" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="K9" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L9" s="3"/>
       <x:c r="N9" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="O9" s="1"/>
       <x:c r="P9" s="3"/>
       <x:c r="R9" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="S9" s="1"/>
       <x:c r="T9" s="3"/>
       <x:c r="V9" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="W9" s="1"/>
       <x:c r="X9" s="3"/>
       <x:c r="Z9" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="AA9" s="1"/>
       <x:c r="AB9" s="3"/>
       <x:c r="AD9" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="AE9" s="1"/>
       <x:c r="AF9" s="3"/>
@@ -1539,7 +1539,7 @@
     <x:row r="10" spans="2:32">
       <x:c r="B10" s="6"/>
       <x:c r="C10" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D10" s="3"/>
       <x:c r="F10" s="7"/>
@@ -1569,80 +1569,80 @@
     </x:row>
     <x:row r="13" spans="2:4">
       <x:c r="B13" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="2:4">
       <x:c r="B14" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C14" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D14" s="3"/>
     </x:row>
     <x:row r="15" spans="2:4">
       <x:c r="B15" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D15" s="3"/>
     </x:row>
     <x:row r="16" spans="2:4">
       <x:c r="B16" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C16" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D16" s="3"/>
     </x:row>
     <x:row r="17" spans="2:4">
       <x:c r="B17" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D17" s="3"/>
     </x:row>
     <x:row r="18" spans="2:4">
       <x:c r="B18" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C18" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D18" s="3"/>
     </x:row>
     <x:row r="19" spans="2:4">
       <x:c r="B19" s="7"/>
       <x:c r="C19" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D19" s="3"/>
     </x:row>
     <x:row r="20" spans="2:4">
       <x:c r="B20" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D20" s="3"/>
     </x:row>
     <x:row r="21" spans="2:4">
       <x:c r="B21" s="7"/>
       <x:c r="C21" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D21" s="3"/>
     </x:row>
@@ -1651,70 +1651,70 @@
     </x:row>
     <x:row r="24" spans="2:4">
       <x:c r="B24" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C24" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D24" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="2:4">
       <x:c r="B25" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C25" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D25" s="3"/>
     </x:row>
     <x:row r="26" spans="2:4">
       <x:c r="B26" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D26" s="3"/>
     </x:row>
     <x:row r="27" spans="2:4">
       <x:c r="B27" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C27" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D27" s="3"/>
     </x:row>
     <x:row r="28" spans="2:4">
       <x:c r="B28" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C28" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D28" s="3"/>
     </x:row>
     <x:row r="29" spans="2:4">
       <x:c r="B29" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C29" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D29" s="3"/>
     </x:row>
     <x:row r="30" spans="2:4">
       <x:c r="B30" s="7"/>
       <x:c r="C30" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D30" s="3"/>
     </x:row>
     <x:row r="31" spans="2:4">
       <x:c r="B31" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>28</x:v>
@@ -1724,7 +1724,7 @@
     <x:row r="32" spans="2:4">
       <x:c r="B32" s="7"/>
       <x:c r="C32" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D32" s="3"/>
     </x:row>
@@ -1751,7 +1751,7 @@
     <x:mergeCell ref="B29:B30"/>
     <x:mergeCell ref="B31:B32"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>